--- a/job-costing/job-costing-tracker-demo.xlsx
+++ b/job-costing/job-costing-tracker-demo.xlsx
@@ -1016,7 +1016,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  Job Costing Tracker</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  Job Costing Tracker</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  Job Costing Tracker</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  Job Costing Tracker</t>
         </is>
       </c>
     </row>
